--- a/makeup_artist_forms/002_permanent_makeup_client_information_form--makeup_artist_forms.xlsx
+++ b/makeup_artist_forms/002_permanent_makeup_client_information_form--makeup_artist_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1126,7 +1126,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C23"/>
+  <dimension ref="A1:C21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -1278,46 +1278,46 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>eyeliner</t>
+          <t>eyebrow_microblading</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Eyeliner</t>
+          <t>Eyebrow Microblading</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>desired_service_choices</t>
+          <t>preferred_artist_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>eyebrow_microblading</t>
+          <t>chat</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Eyebrow Microblading</t>
+          <t>Chat</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>desired_service_choices</t>
+          <t>preferred_artist_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>lip_liner</t>
+          <t>jimmy</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Lip Liner</t>
+          <t>Jimmy</t>
         </is>
       </c>
     </row>
@@ -1329,46 +1329,46 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>chat</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Chat</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>preferred_artist_choices</t>
+          <t>contact_method_choices</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>jimmy</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Jimmy</t>
+          <t>Phone</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>preferred_artist_choices</t>
+          <t>contact_method_choices</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>email</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Email</t>
         </is>
       </c>
     </row>
@@ -1380,46 +1380,46 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>phone</t>
+          <t>text</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Phone</t>
+          <t>Text</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>contact_method_choices</t>
+          <t>contact_preferred_method_choices</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>email</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Email</t>
+          <t>Phone</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>contact_method_choices</t>
+          <t>contact_preferred_method_choices</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>email</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Text</t>
+          <t>Email</t>
         </is>
       </c>
     </row>
@@ -1431,46 +1431,46 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>phone</t>
+          <t>text</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Phone</t>
+          <t>Text</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>contact_preferred_method_choices</t>
+          <t>appointment_method_choices</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>email</t>
+          <t>in_person</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Email</t>
+          <t>In person</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>contact_preferred_method_choices</t>
+          <t>appointment_method_choices</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>over_video_call</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Text</t>
+          <t>Over video call</t>
         </is>
       </c>
     </row>
@@ -1482,44 +1482,10 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>in_person</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
-        <is>
-          <t>In person</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>appointment_method_choices</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>over_video_call</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Over video call</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>appointment_method_choices</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>other</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
         <is>
           <t>Other</t>
         </is>
